--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HOTEL 4POSTES - ÁVILA AUTÉNTICA - EL BULEVAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HOTEL 4POSTES - ÁVILA AUTÉNTICA - EL BULEVAR.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>49.7502</v>
+        <v>63.2018</v>
       </c>
       <c r="E2" t="n">
-        <v>29.5341</v>
+        <v>61.61340000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>20.2167</v>
+        <v>1.588499999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5848</v>
+        <v>27.4317</v>
       </c>
       <c r="H2" t="n">
-        <v>13.7491</v>
+        <v>6.234699999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-8.164199999999999</v>
+        <v>21.1971</v>
       </c>
       <c r="J2" t="n">
-        <v>35.1667</v>
+        <v>58.6757</v>
       </c>
       <c r="K2" t="n">
-        <v>34.7573</v>
+        <v>29.4197</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4096999999999999</v>
+        <v>29.256</v>
       </c>
       <c r="M2" t="n">
-        <v>-29.5823</v>
+        <v>-31.2438</v>
       </c>
       <c r="N2" t="n">
-        <v>-21.0086</v>
+        <v>-23.1853</v>
       </c>
       <c r="O2" t="n">
-        <v>-8.573500000000001</v>
+        <v>-8.0588</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.3339</v>
+        <v>-0.1930000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-61.5695</v>
+        <v>-58.8673</v>
       </c>
       <c r="R2" t="n">
-        <v>54.2353</v>
+        <v>58.6747</v>
       </c>
       <c r="S2" t="n">
-        <v>33.8675</v>
+        <v>0.2289999999999998</v>
       </c>
       <c r="T2" t="n">
-        <v>20.6832</v>
+        <v>1.2417</v>
       </c>
       <c r="U2" t="n">
-        <v>13.1839</v>
+        <v>-1.0129</v>
       </c>
       <c r="V2" t="n">
-        <v>17.6326</v>
+        <v>35.7339</v>
       </c>
       <c r="W2" t="n">
-        <v>35.2537</v>
+        <v>60.5635</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.6208</v>
+        <v>-24.8294</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>36.8966</v>
+        <v>52.4178</v>
       </c>
       <c r="E3" t="n">
-        <v>43.2776</v>
+        <v>39.0859</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.3811</v>
+        <v>13.3313</v>
       </c>
       <c r="G3" t="n">
-        <v>27.4317</v>
+        <v>28.1564</v>
       </c>
       <c r="H3" t="n">
-        <v>6.234699999999999</v>
+        <v>16.6233</v>
       </c>
       <c r="I3" t="n">
-        <v>21.1971</v>
+        <v>11.5329</v>
       </c>
       <c r="J3" t="n">
-        <v>58.6757</v>
+        <v>56.0316</v>
       </c>
       <c r="K3" t="n">
-        <v>29.4197</v>
+        <v>36.676</v>
       </c>
       <c r="L3" t="n">
-        <v>29.256</v>
+        <v>19.3556</v>
       </c>
       <c r="M3" t="n">
-        <v>-31.2438</v>
+        <v>-27.8752</v>
       </c>
       <c r="N3" t="n">
-        <v>-23.1853</v>
+        <v>-20.0529</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.0588</v>
+        <v>-7.8223</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1930000000000001</v>
+        <v>7.527599999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-58.8673</v>
+        <v>-47.0936</v>
       </c>
       <c r="R3" t="n">
-        <v>58.6747</v>
+        <v>54.6215</v>
       </c>
       <c r="S3" t="n">
-        <v>-26.0756</v>
+        <v>0.5201999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-17.0939</v>
+        <v>-0.7745000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.981999999999999</v>
+        <v>1.2947</v>
       </c>
       <c r="V3" t="n">
-        <v>35.7339</v>
+        <v>16.2135</v>
       </c>
       <c r="W3" t="n">
-        <v>60.5635</v>
+        <v>30.9233</v>
       </c>
       <c r="X3" t="n">
-        <v>-24.8294</v>
+        <v>-14.7097</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>32.3666</v>
+        <v>35.0354</v>
       </c>
       <c r="E4" t="n">
-        <v>26.4963</v>
+        <v>20.3935</v>
       </c>
       <c r="F4" t="n">
-        <v>5.870399999999999</v>
+        <v>14.642</v>
       </c>
       <c r="G4" t="n">
-        <v>28.1564</v>
+        <v>5.5848</v>
       </c>
       <c r="H4" t="n">
-        <v>16.6233</v>
+        <v>13.7491</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5329</v>
+        <v>-8.164199999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>56.0316</v>
+        <v>35.1667</v>
       </c>
       <c r="K4" t="n">
-        <v>36.676</v>
+        <v>34.7573</v>
       </c>
       <c r="L4" t="n">
-        <v>19.3556</v>
+        <v>0.4096999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-27.8752</v>
+        <v>-29.5823</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.0529</v>
+        <v>-21.0086</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.8223</v>
+        <v>-8.573500000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>7.527599999999999</v>
+        <v>-7.3339</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.0936</v>
+        <v>-61.5695</v>
       </c>
       <c r="R4" t="n">
-        <v>54.6215</v>
+        <v>54.2353</v>
       </c>
       <c r="S4" t="n">
-        <v>-19.5307</v>
+        <v>19.1521</v>
       </c>
       <c r="T4" t="n">
-        <v>-13.3645</v>
+        <v>11.5429</v>
       </c>
       <c r="U4" t="n">
-        <v>-6.1662</v>
+        <v>7.6096</v>
       </c>
       <c r="V4" t="n">
-        <v>16.2135</v>
+        <v>17.6326</v>
       </c>
       <c r="W4" t="n">
-        <v>30.9233</v>
+        <v>35.2537</v>
       </c>
       <c r="X4" t="n">
-        <v>-14.7097</v>
+        <v>-17.6208</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>24.1036</v>
+        <v>18.3333</v>
       </c>
       <c r="E5" t="n">
-        <v>24.1579</v>
+        <v>15.8214</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.05440000000000067</v>
+        <v>2.5119</v>
       </c>
       <c r="G5" t="n">
         <v>2.5518</v>
@@ -844,13 +844,13 @@
         <v>28.5649</v>
       </c>
       <c r="S5" t="n">
-        <v>14.8517</v>
+        <v>9.081799999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>18.052</v>
+        <v>9.7158</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.2004</v>
+        <v>-0.6337999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>1.2955</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>T. TAPÉ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>18.4975</v>
+        <v>9.936199999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>12.4036</v>
+        <v>7.328900000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>6.094200000000001</v>
+        <v>2.6075</v>
       </c>
       <c r="G6" t="n">
-        <v>10.6933</v>
+        <v>-3.080900000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0013</v>
+        <v>2.0929</v>
       </c>
       <c r="I6" t="n">
-        <v>8.692</v>
+        <v>-5.1738</v>
       </c>
       <c r="J6" t="n">
-        <v>27.6366</v>
+        <v>9.2959</v>
       </c>
       <c r="K6" t="n">
-        <v>17.031</v>
+        <v>9.2401</v>
       </c>
       <c r="L6" t="n">
-        <v>10.6063</v>
+        <v>0.05579999999999993</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.9435</v>
+        <v>-12.3767</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.0298</v>
+        <v>-7.1472</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9142</v>
+        <v>-5.2295</v>
       </c>
       <c r="P6" t="n">
-        <v>-9.0715</v>
+        <v>1.3511</v>
       </c>
       <c r="Q6" t="n">
-        <v>-51.53279999999999</v>
+        <v>-17.5637</v>
       </c>
       <c r="R6" t="n">
-        <v>42.4618</v>
+        <v>18.9148</v>
       </c>
       <c r="S6" t="n">
-        <v>39.1437</v>
+        <v>4.2563</v>
       </c>
       <c r="T6" t="n">
-        <v>29.7347</v>
+        <v>1.8878</v>
       </c>
       <c r="U6" t="n">
-        <v>9.4091</v>
+        <v>2.3685</v>
       </c>
       <c r="V6" t="n">
-        <v>-22.268</v>
+        <v>7.4101</v>
       </c>
       <c r="W6" t="n">
-        <v>6.5652</v>
+        <v>13.7091</v>
       </c>
       <c r="X6" t="n">
-        <v>-28.8331</v>
+        <v>-6.299</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>15.6096</v>
+        <v>5.903</v>
       </c>
       <c r="E7" t="n">
-        <v>9.445799999999998</v>
+        <v>0.8118999999999994</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1637</v>
+        <v>5.0911</v>
       </c>
       <c r="G7" t="n">
         <v>0.5029000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>16.0197</v>
       </c>
       <c r="S7" t="n">
-        <v>19.4596</v>
+        <v>9.752800000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>16.4485</v>
+        <v>7.8144</v>
       </c>
       <c r="U7" t="n">
-        <v>3.0112</v>
+        <v>1.9384</v>
       </c>
       <c r="V7" t="n">
         <v>0.08640000000000037</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. TAPÉ</t>
+          <t>J. HORCAJO GARCÍA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>12.4997</v>
+        <v>4.3644</v>
       </c>
       <c r="E8" t="n">
-        <v>10.0762</v>
+        <v>1.2144</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4232</v>
+        <v>3.15</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.080900000000001</v>
+        <v>0.33</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0929</v>
+        <v>-1.4137</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.1738</v>
+        <v>1.7436</v>
       </c>
       <c r="J8" t="n">
-        <v>9.2959</v>
+        <v>1.1371</v>
       </c>
       <c r="K8" t="n">
-        <v>9.2401</v>
+        <v>-0.2381</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05579999999999993</v>
+        <v>1.3753</v>
       </c>
       <c r="M8" t="n">
-        <v>-12.3767</v>
+        <v>-0.8070999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.1472</v>
+        <v>-1.1756</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.2295</v>
+        <v>0.3683999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3511</v>
+        <v>4.0531</v>
       </c>
       <c r="Q8" t="n">
-        <v>-17.5637</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>18.9148</v>
+        <v>5.0182</v>
       </c>
       <c r="S8" t="n">
-        <v>6.8194</v>
+        <v>1.2093</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6353</v>
+        <v>1.0425</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1843</v>
+        <v>0.1668</v>
       </c>
       <c r="V8" t="n">
-        <v>7.4101</v>
+        <v>-1.228</v>
       </c>
       <c r="W8" t="n">
-        <v>13.7091</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.299</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. HORCAJO GARCÍA</t>
+          <t>A. RUIZ FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>4.9855</v>
+        <v>2.795299999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1563</v>
+        <v>7.1553</v>
       </c>
       <c r="F9" t="n">
-        <v>2.829</v>
+        <v>-4.3602</v>
       </c>
       <c r="G9" t="n">
-        <v>0.33</v>
+        <v>5.606599999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4137</v>
+        <v>-0.5141999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7436</v>
+        <v>6.1204</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1371</v>
+        <v>11.4121</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2381</v>
+        <v>4.6417</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3753</v>
+        <v>6.7706</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8070999999999999</v>
+        <v>-5.8053</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1756</v>
+        <v>-5.1559</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3683999999999999</v>
+        <v>-0.6500999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>4.0531</v>
+        <v>-1.158</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>-6.7552</v>
       </c>
       <c r="R9" t="n">
-        <v>5.0182</v>
+        <v>5.5971</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8303</v>
+        <v>-1.884</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9844</v>
+        <v>-0.2011</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.154</v>
+        <v>-1.683</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.228</v>
+        <v>0.2306</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.6997</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.228</v>
+        <v>-2.469</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9622000000000002</v>
+        <v>1.4085</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7688</v>
+        <v>1.1882</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1933000000000001</v>
+        <v>0.2202</v>
       </c>
       <c r="G10" t="n">
         <v>0.9183</v>
@@ -1234,13 +1234,13 @@
         <v>1.93</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6353</v>
+        <v>-0.1892</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6397999999999999</v>
+        <v>-0.2204</v>
       </c>
       <c r="U10" t="n">
-        <v>0.004599999999999993</v>
+        <v>0.03139999999999998</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2859</v>
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4277</v>
+        <v>0.2801</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3107</v>
+        <v>0.9116</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7384000000000001</v>
+        <v>-0.6314</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4687999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7311</v>
+        <v>-0.0231</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4019</v>
+        <v>0.199</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3292</v>
+        <v>-0.2221</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RUIZ FERNÁNDEZ</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.510300000000001</v>
+        <v>-1.934099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>4.054</v>
+        <v>2.827</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.5644</v>
+        <v>-4.7612</v>
       </c>
       <c r="G12" t="n">
-        <v>5.606599999999999</v>
+        <v>-4.6201</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5141999999999999</v>
+        <v>-1.0826</v>
       </c>
       <c r="I12" t="n">
-        <v>6.1204</v>
+        <v>-3.5374</v>
       </c>
       <c r="J12" t="n">
-        <v>11.4121</v>
+        <v>14.0501</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6417</v>
+        <v>11.89</v>
       </c>
       <c r="L12" t="n">
-        <v>6.7706</v>
+        <v>2.1598</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.8053</v>
+        <v>-18.6699</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.1559</v>
+        <v>-12.9725</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6500999999999999</v>
+        <v>-5.6972</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.158</v>
+        <v>7.9133</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.7552</v>
+        <v>-33.5834</v>
       </c>
       <c r="R12" t="n">
-        <v>5.5971</v>
+        <v>41.4969</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.1894</v>
+        <v>5.3095</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.3023</v>
+        <v>2.839799999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8873</v>
+        <v>2.4698</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2306</v>
+        <v>-10.5368</v>
       </c>
       <c r="W12" t="n">
-        <v>2.6997</v>
+        <v>19.5209</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.469</v>
+        <v>-30.0575</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ CRESPO</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8119</v>
+        <v>-3.7693</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6292</v>
+        <v>-4.9512</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1828</v>
+        <v>1.1819</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7175</v>
+        <v>-5.043299999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2545</v>
+        <v>-0.8477999999999994</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5369</v>
+        <v>-4.1953</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.978</v>
+        <v>6.0129</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9938</v>
+        <v>9.004</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0158</v>
+        <v>-2.990599999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2606000000000001</v>
+        <v>-11.0561</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2606999999999999</v>
+        <v>-9.8514</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5212</v>
+        <v>-1.2045</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.772</v>
+        <v>1.544099999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.8951</v>
+        <v>-17.5635</v>
       </c>
       <c r="R13" t="n">
-        <v>2.123</v>
+        <v>19.1073</v>
       </c>
       <c r="S13" t="n">
-        <v>1.277</v>
+        <v>3.8374</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2441</v>
+        <v>4.9268</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03300000000000003</v>
+        <v>-1.0893</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.5993</v>
+        <v>-4.107699999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.6731</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.5993</v>
+        <v>-5.7809</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.9556</v>
+        <v>-4.210499999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.6303</v>
+        <v>-6.3912</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6745999999999999</v>
+        <v>2.180599999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.043299999999999</v>
+        <v>10.6933</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8477999999999994</v>
+        <v>2.0013</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.1953</v>
+        <v>8.692</v>
       </c>
       <c r="J14" t="n">
-        <v>6.0129</v>
+        <v>27.6366</v>
       </c>
       <c r="K14" t="n">
-        <v>9.004</v>
+        <v>17.031</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.990599999999999</v>
+        <v>10.6063</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.0561</v>
+        <v>-16.9435</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.8514</v>
+        <v>-15.0298</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2045</v>
+        <v>-1.9142</v>
       </c>
       <c r="P14" t="n">
-        <v>1.544099999999999</v>
+        <v>-9.0715</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.5635</v>
+        <v>-51.53279999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>19.1073</v>
+        <v>42.4618</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6512</v>
+        <v>16.4354</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2474</v>
+        <v>10.9399</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5962</v>
+        <v>5.4954</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.107699999999999</v>
+        <v>-22.268</v>
       </c>
       <c r="W14" t="n">
-        <v>1.6731</v>
+        <v>6.5652</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.7809</v>
+        <v>-28.8331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. ELKSNIS</t>
+          <t>A. FERNANDEZ CRESPO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-10.4802</v>
+        <v>-4.6021</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.0497</v>
+        <v>-3.1516</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.430499999999999</v>
+        <v>-1.4505</v>
       </c>
       <c r="G15" t="n">
-        <v>-12.1901</v>
+        <v>-0.7175</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.832699999999999</v>
+        <v>-1.2545</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.3572</v>
+        <v>0.5369</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.3459</v>
+        <v>-0.978</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7108</v>
+        <v>-0.9938</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.0565</v>
+        <v>0.0158</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.8443</v>
+        <v>0.2606000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-9.543600000000001</v>
+        <v>-0.2606999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3007000000000002</v>
+        <v>0.5212</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1581</v>
+        <v>-0.772</v>
       </c>
       <c r="Q15" t="n">
-        <v>-11.0013</v>
+        <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
-        <v>9.843299999999999</v>
+        <v>2.123</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3572</v>
+        <v>0.4868</v>
       </c>
       <c r="T15" t="n">
-        <v>4.6404</v>
+        <v>0.7216</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2833</v>
+        <v>-0.2347</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4891999999999997</v>
+        <v>-3.5993</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6573</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.1467</v>
+        <v>-3.5993</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-16.4995</v>
+        <v>-6.085899999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.3423</v>
+        <v>-22.5975</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.157499999999999</v>
+        <v>16.5115</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.6201</v>
+        <v>-4.890899999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0826</v>
+        <v>-5.1786</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.5374</v>
+        <v>0.2877000000000003</v>
       </c>
       <c r="J16" t="n">
-        <v>14.0501</v>
+        <v>4.7177</v>
       </c>
       <c r="K16" t="n">
-        <v>11.89</v>
+        <v>5.390899999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1598</v>
+        <v>-0.6726999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-18.6699</v>
+        <v>-9.608499999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-12.9725</v>
+        <v>-10.5689</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.6972</v>
+        <v>0.9605000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9133</v>
+        <v>12.7382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-33.5834</v>
+        <v>-29.9159</v>
       </c>
       <c r="R16" t="n">
-        <v>41.4969</v>
+        <v>42.6548</v>
       </c>
       <c r="S16" t="n">
-        <v>-9.255699999999999</v>
+        <v>0.2219000000000002</v>
       </c>
       <c r="T16" t="n">
-        <v>-8.3292</v>
+        <v>0.1130000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9268999999999999</v>
+        <v>0.1088000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-10.5368</v>
+        <v>-14.1555</v>
       </c>
       <c r="W16" t="n">
-        <v>19.5209</v>
+        <v>2.4884</v>
       </c>
       <c r="X16" t="n">
-        <v>-30.0575</v>
+        <v>-16.644</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>R. ELKSNIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>-17.4473</v>
+        <v>-13.3448</v>
       </c>
       <c r="E17" t="n">
-        <v>-28.6375</v>
+        <v>-9.635899999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>11.1902</v>
+        <v>-3.7091</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.890899999999999</v>
+        <v>-12.1901</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.1786</v>
+        <v>-6.832699999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2877000000000003</v>
+        <v>-5.3572</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7177</v>
+        <v>-2.3459</v>
       </c>
       <c r="K17" t="n">
-        <v>5.390899999999999</v>
+        <v>2.7108</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6726999999999999</v>
+        <v>-5.0565</v>
       </c>
       <c r="M17" t="n">
-        <v>-9.608499999999999</v>
+        <v>-9.8443</v>
       </c>
       <c r="N17" t="n">
-        <v>-10.5689</v>
+        <v>-9.543600000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9605000000000001</v>
+        <v>-0.3007000000000002</v>
       </c>
       <c r="P17" t="n">
-        <v>12.7382</v>
+        <v>-1.1581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-29.9159</v>
+        <v>-11.0013</v>
       </c>
       <c r="R17" t="n">
-        <v>42.6548</v>
+        <v>9.843299999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.1397</v>
+        <v>0.4924999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-5.9272</v>
+        <v>1.0542</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.2126</v>
+        <v>-0.5615</v>
       </c>
       <c r="V17" t="n">
-        <v>-14.1555</v>
+        <v>-0.4891999999999997</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4884</v>
+        <v>2.6573</v>
       </c>
       <c r="X17" t="n">
-        <v>-16.644</v>
+        <v>-3.1467</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-21.9738</v>
+        <v>-15.0319</v>
       </c>
       <c r="E18" t="n">
-        <v>-18.7969</v>
+        <v>-13.5925</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.1771</v>
+        <v>-1.4391</v>
       </c>
       <c r="G18" t="n">
         <v>-3.454800000000001</v>
@@ -1858,13 +1858,13 @@
         <v>16.7915</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.5453</v>
+        <v>3.3964</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.0008</v>
+        <v>2.2037</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5448999999999999</v>
+        <v>1.1927</v>
       </c>
       <c r="V18" t="n">
         <v>-11.3066</v>
@@ -1891,22 +1891,22 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>116.5652</v>
+        <v>144.6972</v>
       </c>
       <c r="E19" t="n">
-        <v>90.59539999999998</v>
+        <v>98.03160000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>25.9691</v>
+        <v>46.665</v>
       </c>
       <c r="G19" t="n">
         <v>47.3094</v>
       </c>
       <c r="H19" t="n">
-        <v>25.8742</v>
+        <v>25.87420000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>21.43540000000001</v>
+        <v>21.4354</v>
       </c>
       <c r="J19" t="n">
         <v>254.3891</v>
@@ -1915,7 +1915,7 @@
         <v>186.1866</v>
       </c>
       <c r="L19" t="n">
-        <v>68.20529999999999</v>
+        <v>68.20530000000001</v>
       </c>
       <c r="M19" t="n">
         <v>-207.0795</v>
@@ -1930,19 +1930,19 @@
         <v>14.4758</v>
       </c>
       <c r="Q19" t="n">
-        <v>-404.3493</v>
+        <v>-404.3492999999999</v>
       </c>
       <c r="R19" t="n">
         <v>418.8268</v>
       </c>
       <c r="S19" t="n">
-        <v>44.15480000000001</v>
+        <v>72.2851</v>
       </c>
       <c r="T19" t="n">
-        <v>47.6104</v>
+        <v>55.0471</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.456899999999999</v>
+        <v>17.2388</v>
       </c>
       <c r="V19" t="n">
         <v>10.6256</v>
